--- a/data/case-study-comparing-marketing-channels--marketing_channels.xlsx
+++ b/data/case-study-comparing-marketing-channels--marketing_channels.xlsx
@@ -6215,7 +6215,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: customers acquired through four marketing channels with their 90-day revenue.</t>
+          <t>WHAT IS CAPTURED: customers acquired through four marketing channels with their 90-day revenue (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
